--- a/docs/dossiers/dossier-local-commercial-81-m2-paris-11eme-fee6d7ab.xlsx
+++ b/docs/dossiers/dossier-local-commercial-81-m2-paris-11eme-fee6d7ab.xlsx
@@ -2266,7 +2266,7 @@
       </c>
       <c r="B7" s="30" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Extraction / vraie restauration possible</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="B10" s="30" t="inlineStr">
         <is>
-          <t>Décote sans explication visible dans l'annonce : possible bonne affaire — ou défaut caché (état, copropriété, bail) à vérifier sur place.</t>
+          <t>Décote lisible : des travaux sont signalés dans l'annonce.</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="B12" s="30" t="inlineStr">
         <is>
-          <t>1 nouvelle annonce dans votre zone personnalisée : Paris Votre recherche : Vente &gt; Boutique, Local commercial &gt; Paris &gt; Maximum 300,000 € 299 000 € Local commercial 81 m² Paris 11ème (75011) GROUPE BABYLONE Bureaux Voir l'annonce Se désinscrire | Nous contacter Cet e-mail vous a été envoyé sur georgesdurand75+lesmurs@gmail.com parce que vous avez souscrit à une alerte sur SeLoger</t>
+          <t>À vendre : une opportunité rare au coeur de Paris pour les entrepreneurs et investisseurs à la recherche d'un espace commercial unique. Situé dans un quartier dynamique et prisé de la capitale, ce local commercial offre un potentiel exceptionnel pour ceux qui souhaitent s'implanter dans l'une des villes les plus attractives du monde. Anciennement un bar, ce bien conserve le charme et l'authenticité des établissements parisiens traditionnels, tout en offrant la possibilité de le transformer selon vos besoins et aspirations. Le local, à rénover, se compose d'un plateau principal de 40 m² en rez-de-chaussée, idéal pour accueillir votre activité commerciale, qu'il s'agisse d'une boutique, d'un café ou d'un espace de coworking. Le sous-sol, d'une superficie de 41 m², était autrefois la cave de l'immeuble et est accessible à la fois par les parties communes et directement depuis le local, offrant ainsi une flexibilité d'aménagement supplémentaire. Bien que le local ne dispose pas d'une extraction, il reste parfaitement adapté pour de nombreuses activités commerciales qui ne nécessitent pas cette installation spécifique. L'absence d'extraction peut également être vue comme une opportunité de se démarquer en proposant un concept innovant qui s'intègre harmonieusement dans le tissu urbain environnant. La localisation centrale de ce bien est un atout majeur, bénéficiant d'une forte visibilité et d'un passage piétonnier important, ce qui est idéal pour attirer une clientèle variée et nombreuse. De plus, la proximité des transports en commun facilite l'accès pour vos clients et collaborateurs. Ce local est une toile vierge qui n'attend que votre vision pour prendre vie. Que vous soyez un restaurateur souhaitant créer un espace convivial et chaleureux, un détaillant cherchant à établir une boutique tendance, ou un entrepreneur en quête d'un lieu inspirant pour développer votre activité, ce bien offre une multitude de possibilités. Ne manquez pas cette chance de devenir propriéta</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-local-commercial-81-m2-paris-11eme-fee6d7ab.xlsx
+++ b/docs/dossiers/dossier-local-commercial-81-m2-paris-11eme-fee6d7ab.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 14/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 15/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-local-commercial-81-m2-paris-11eme-fee6d7ab.xlsx
+++ b/docs/dossiers/dossier-local-commercial-81-m2-paris-11eme-fee6d7ab.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 15/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 16/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-local-commercial-81-m2-paris-11eme-fee6d7ab.xlsx
+++ b/docs/dossiers/dossier-local-commercial-81-m2-paris-11eme-fee6d7ab.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 16/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 17/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-local-commercial-81-m2-paris-11eme-fee6d7ab.xlsx
+++ b/docs/dossiers/dossier-local-commercial-81-m2-paris-11eme-fee6d7ab.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 17/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 18/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-local-commercial-81-m2-paris-11eme-fee6d7ab.xlsx
+++ b/docs/dossiers/dossier-local-commercial-81-m2-paris-11eme-fee6d7ab.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 18/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 19/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-local-commercial-81-m2-paris-11eme-fee6d7ab.xlsx
+++ b/docs/dossiers/dossier-local-commercial-81-m2-paris-11eme-fee6d7ab.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 19/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 20/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-local-commercial-81-m2-paris-11eme-fee6d7ab.xlsx
+++ b/docs/dossiers/dossier-local-commercial-81-m2-paris-11eme-fee6d7ab.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 20/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 21/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-local-commercial-81-m2-paris-11eme-fee6d7ab.xlsx
+++ b/docs/dossiers/dossier-local-commercial-81-m2-paris-11eme-fee6d7ab.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 21/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 22/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-local-commercial-81-m2-paris-11eme-fee6d7ab.xlsx
+++ b/docs/dossiers/dossier-local-commercial-81-m2-paris-11eme-fee6d7ab.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 22/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 23/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-local-commercial-81-m2-paris-11eme-fee6d7ab.xlsx
+++ b/docs/dossiers/dossier-local-commercial-81-m2-paris-11eme-fee6d7ab.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 23/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 24/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-local-commercial-81-m2-paris-11eme-fee6d7ab.xlsx
+++ b/docs/dossiers/dossier-local-commercial-81-m2-paris-11eme-fee6d7ab.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 24/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 25/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-local-commercial-81-m2-paris-11eme-fee6d7ab.xlsx
+++ b/docs/dossiers/dossier-local-commercial-81-m2-paris-11eme-fee6d7ab.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Annonce" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Synthèse'!$A$1:$C$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Synthèse'!$A$1:$C$58</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -27,7 +27,7 @@
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="#,##0&quot; €/mois&quot;"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -71,11 +71,6 @@
       <name val="Calibri"/>
       <b val="1"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="0098351B"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -140,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
@@ -154,11 +149,11 @@
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -176,17 +171,14 @@
     <xf numFmtId="168" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -801,7 +793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -937,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 5,34 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +537 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 5,34 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +269 €/mois.</t>
         </is>
       </c>
     </row>
@@ -999,7 +991,7 @@
         </is>
       </c>
       <c r="B20" s="18" t="n">
-        <v>2671.65</v>
+        <v>2362.5</v>
       </c>
       <c r="C20" s="19" t="inlineStr">
         <is>
@@ -1395,7 +1387,7 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>64/100</t>
+          <t>66/100</t>
         </is>
       </c>
       <c r="C57" s="19" t="inlineStr">
@@ -1404,20 +1396,11 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="27" t="inlineStr">
-        <is>
-          <t>⚠ AVERTISSEMENT : le rendement affiché par le vendeur est anormalement élevé. Exiger le bail et les quittances avant toute offre — ce dossier reprend le loyer annoncé tel quel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60"/>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="11">
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A59:C60"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A13:C14"/>
     <mergeCell ref="A34:C34"/>
@@ -1494,27 +1477,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="28" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>Année</t>
         </is>
       </c>
-      <c r="B1" s="28" t="inlineStr">
+      <c r="B1" s="27" t="inlineStr">
         <is>
           <t>Capital dû en début d'année</t>
         </is>
       </c>
-      <c r="C1" s="28" t="inlineStr">
+      <c r="C1" s="27" t="inlineStr">
         <is>
           <t>Intérêts de l'année</t>
         </is>
       </c>
-      <c r="D1" s="28" t="inlineStr">
+      <c r="D1" s="27" t="inlineStr">
         <is>
           <t>Capital remboursé</t>
         </is>
       </c>
-      <c r="E1" s="28" t="inlineStr">
+      <c r="E1" s="27" t="inlineStr">
         <is>
           <t>Capital restant dû</t>
         </is>
@@ -2187,144 +2170,144 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t>Titre</t>
         </is>
       </c>
-      <c r="B1" s="30" t="inlineStr">
+      <c r="B1" s="29" t="inlineStr">
         <is>
           <t>1 nouvelle annonce dans votre zone personnalisée : Paris</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="29" t="inlineStr">
+      <c r="A2" s="28" t="inlineStr">
         <is>
           <t>Lien</t>
         </is>
       </c>
-      <c r="B2" s="31" t="inlineStr">
+      <c r="B2" s="30" t="inlineStr">
         <is>
           <t>https://www.seloger-bureaux-commerces.com/annonce/detail/direct/282344709</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="29" t="inlineStr">
+      <c r="A3" s="28" t="inlineStr">
         <is>
           <t>Ville</t>
         </is>
       </c>
-      <c r="B3" s="30" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>Local commercial 81 m² Paris 11ème (75011)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="B4" s="30" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>alerte_seloger_bureaux</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>Première détection</t>
         </is>
       </c>
-      <c r="B5" s="30" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B6" s="30" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Murs libres</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>Caractéristiques</t>
         </is>
       </c>
-      <c r="B7" s="30" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Extraction / vraie restauration possible</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>Évolution du prix</t>
         </is>
       </c>
-      <c r="B8" s="30" t="inlineStr">
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t>stable depuis la première vue</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="28" t="inlineStr">
         <is>
           <t>Fourchette de marché</t>
         </is>
       </c>
-      <c r="B9" s="30" t="inlineStr">
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t>572 ventes réelles 2023-2025 (DVF)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>Lecture du prix</t>
         </is>
       </c>
-      <c r="B10" s="30" t="inlineStr">
+      <c r="B10" s="29" t="inlineStr">
         <is>
           <t>Décote lisible : des travaux sont signalés dans l'annonce.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>Alertes</t>
         </is>
       </c>
-      <c r="B11" s="30" t="inlineStr">
-        <is>
-          <t>localisation_incoherente · loyer_estime · rendement_anormalement_eleve</t>
+      <c r="B11" s="29" t="inlineStr">
+        <is>
+          <t>localisation_incoherente · loyer_estime</t>
         </is>
       </c>
     </row>
     <row r="12" ht="110" customHeight="1">
-      <c r="A12" s="29" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="B12" s="30" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>À vendre : une opportunité rare au coeur de Paris pour les entrepreneurs et investisseurs à la recherche d'un espace commercial unique. Situé dans un quartier dynamique et prisé de la capitale, ce local commercial offre un potentiel exceptionnel pour ceux qui souhaitent s'implanter dans l'une des villes les plus attractives du monde. Anciennement un bar, ce bien conserve le charme et l'authenticité des établissements parisiens traditionnels, tout en offrant la possibilité de le transformer selon vos besoins et aspirations. Le local, à rénover, se compose d'un plateau principal de 40 m² en rez-de-chaussée, idéal pour accueillir votre activité commerciale, qu'il s'agisse d'une boutique, d'un café ou d'un espace de coworking. Le sous-sol, d'une superficie de 41 m², était autrefois la cave de l'immeuble et est accessible à la fois par les parties communes et directement depuis le local, offrant ainsi une flexibilité d'aménagement supplémentaire. Bien que le local ne dispose pas d'une extraction, il reste parfaitement adapté pour de nombreuses activités commerciales qui ne nécessitent pas cette installation spécifique. L'absence d'extraction peut également être vue comme une opportunité de se démarquer en proposant un concept innovant qui s'intègre harmonieusement dans le tissu urbain environnant. La localisation centrale de ce bien est un atout majeur, bénéficiant d'une forte visibilité et d'un passage piétonnier important, ce qui est idéal pour attirer une clientèle variée et nombreuse. De plus, la proximité des transports en commun facilite l'accès pour vos clients et collaborateurs. Ce local est une toile vierge qui n'attend que votre vision pour prendre vie. Que vous soyez un restaurateur souhaitant créer un espace convivial et chaleureux, un détaillant cherchant à établir une boutique tendance, ou un entrepreneur en quête d'un lieu inspirant pour développer votre activité, ce bien offre une multitude de possibilités. Ne manquez pas cette chance de devenir propriéta</t>
         </is>

--- a/docs/dossiers/dossier-local-commercial-81-m2-paris-11eme-fee6d7ab.xlsx
+++ b/docs/dossiers/dossier-local-commercial-81-m2-paris-11eme-fee6d7ab.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 25/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 26/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="B11" s="29" t="inlineStr">
         <is>
-          <t>localisation_incoherente · loyer_estime</t>
+          <t>localisation_incoherente · loyer_estime · surface_a_ventiler · occupation_a_confirmer</t>
         </is>
       </c>
     </row>
